--- a/output/graficos_dimensiones/comunal_s_fonasa_a_2021_arica y parinacota.xlsx
+++ b/output/graficos_dimensiones/comunal_s_fonasa_a_2021_arica y parinacota.xlsx
@@ -57,7 +57,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 19:56</t>
+    <t xml:space="preserve">2026-09-09 22:47</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_s_fonasa_a_2021_arica y parinacota.xlsx
+++ b/output/graficos_dimensiones/comunal_s_fonasa_a_2021_arica y parinacota.xlsx
@@ -57,7 +57,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 22:47</t>
+    <t xml:space="preserve">2026-09-18 10:08</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_s_fonasa_a_2021_arica y parinacota.xlsx
+++ b/output/graficos_dimensiones/comunal_s_fonasa_a_2021_arica y parinacota.xlsx
@@ -39,12 +39,12 @@
     <t xml:space="preserve">Arica</t>
   </si>
   <si>
+    <t xml:space="preserve">Camarones</t>
+  </si>
+  <si>
     <t xml:space="preserve">Putre</t>
   </si>
   <si>
-    <t xml:space="preserve">Camarones</t>
-  </si>
-  <si>
     <t xml:space="preserve">General Lagos</t>
   </si>
   <si>
@@ -57,7 +57,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 10:08</t>
+    <t xml:space="preserve">2026-09-23 12:13</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -504,9 +504,11 @@
         <v>7</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>15201</v>
-      </c>
-      <c r="D3" s="2"/>
+        <v>15102</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>2021</v>
+      </c>
       <c r="E3" s="2"/>
     </row>
     <row r="4">
@@ -517,9 +519,11 @@
         <v>8</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>15102</v>
-      </c>
-      <c r="D4" s="2"/>
+        <v>15201</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>2021</v>
+      </c>
       <c r="E4" s="2"/>
     </row>
     <row r="5">
@@ -532,7 +536,9 @@
       <c r="C5" s="2" t="n">
         <v>15202</v>
       </c>
-      <c r="D5" s="2"/>
+      <c r="D5" s="2" t="n">
+        <v>2021</v>
+      </c>
       <c r="E5" s="2"/>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_s_fonasa_a_2021_arica y parinacota.xlsx
+++ b/output/graficos_dimensiones/comunal_s_fonasa_a_2021_arica y parinacota.xlsx
@@ -57,7 +57,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 12:13</t>
+    <t xml:space="preserve">2026-10-02 13:55</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_s_fonasa_a_2021_arica y parinacota.xlsx
+++ b/output/graficos_dimensiones/comunal_s_fonasa_a_2021_arica y parinacota.xlsx
@@ -57,7 +57,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 13:55</t>
+    <t xml:space="preserve">2026-10-05 09:15</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
